--- a/docs/Plantilla_VTC_Valoracion_Despues_del_Hecho.xlsx
+++ b/docs/Plantilla_VTC_Valoracion_Despues_del_Hecho.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INICIO" sheetId="1" r:id="R8fd32dfc4bfa468e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMEN" sheetId="2" r:id="Rabbd1a6578ed476f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CASO" sheetId="3" r:id="R558009ed66c841ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMPONENTES" sheetId="4" r:id="Rf075c7925ae64c52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SERVICIOS_B" sheetId="5" r:id="R58c3a2e0c81c4d7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GRAVEDAD" sheetId="6" r:id="R4d213d0651ba4682"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVISION" sheetId="7" r:id="R85ad3311fdf042ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INICIO" sheetId="1" r:id="Rc20ce371645341cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMEN" sheetId="2" r:id="Rbfd64169e9ed432e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CASO" sheetId="3" r:id="Rcc29881e6f6f4690"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMPONENTES" sheetId="4" r:id="Rea8e18476c724ad9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SERVICIOS_B" sheetId="5" r:id="R02c98cb7465347e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GRAVEDAD" sheetId="6" r:id="R2bb88dbb0dad4d6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVISION" sheetId="7" r:id="R34086a3cc8ea4eac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MULTAS_7317" sheetId="8" r:id="R2d49b66f13634b87"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,14 +20,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="5">
+  <x:numFmts count="7">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="0.0%"/>
     <x:numFmt numFmtId="202" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="203" formatCode="&quot;$&quot;#,##0.00;[Red](&quot;$&quot;#,##0.00);-"/>
     <x:numFmt numFmtId="204" formatCode="0.0000"/>
+    <x:numFmt numFmtId="205" formatCode="[$₡-es-CR]#,##0"/>
+    <x:numFmt numFmtId="206" formatCode="0.00"/>
   </x:numFmts>
-  <x:fonts count="8">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -70,8 +73,14 @@
       <x:color rgb="FF008000"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2933"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -103,6 +112,31 @@
         <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF173A4F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEFEF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF147D80"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -124,7 +158,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="77">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -210,10 +244,128 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="8" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="1">
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF1F2933"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
 </x:styleSheet>
 </file>
 
@@ -579,10 +731,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="18" t="str">
-        <x:v>REVISION</x:v>
+        <x:v>MULTAS_7317</x:v>
       </x:c>
       <x:c r="C10" s="18" t="str">
-        <x:v>Complete los controles y las aprobaciones técnica, económica y jurídica.</x:v>
+        <x:v>Marque las multas aplicables, confirme el salario base y revise el monto.</x:v>
       </x:c>
       <x:c r="D10" s="34"/>
       <x:c r="E10" s="34"/>
@@ -595,10 +747,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B11" s="18" t="str">
-        <x:v>RESUMEN</x:v>
+        <x:v>REVISION</x:v>
       </x:c>
       <x:c r="C11" s="18" t="str">
-        <x:v>Lea el rango, la restauración, lo exploratorio y los controles pendientes.</x:v>
+        <x:v>Complete los controles y las aprobaciones técnica, económica y jurídica.</x:v>
       </x:c>
       <x:c r="D11" s="34"/>
       <x:c r="E11" s="34"/>
@@ -606,10 +758,16 @@
       <x:c r="G11" s="34"/>
       <x:c r="H11" s="34"/>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="34"/>
-      <x:c r="B12" s="34"/>
-      <x:c r="C12" s="34"/>
+    <x:row r="12" ht="22" customHeight="1">
+      <x:c r="A12" s="72" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B12" s="50" t="str">
+        <x:v>RESUMEN</x:v>
+      </x:c>
+      <x:c r="C12" s="50" t="str">
+        <x:v>Lea el daño, la restauración, las multas y el total final.</x:v>
+      </x:c>
       <x:c r="D12" s="34"/>
       <x:c r="E12" s="34"/>
       <x:c r="F12" s="34"/>
@@ -656,7 +814,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="20" t="str">
-        <x:v>2. No use precio ilegal, multa, salario base, UICN o CITES como multiplicador del daño.</x:v>
+        <x:v>2. No use precio ilegal, multa, salario base, UICN o CITES como multiplicador del daño. La multa se registra por separado y solo se suma al cierre.</x:v>
       </x:c>
       <x:c r="B15" s="20"/>
       <x:c r="C15" s="20"/>
@@ -899,7 +1057,7 @@
       </x:c>
       <x:c r="B5" s="30" t="str">
         <x:f>IF(REVISION!B18=0,"Lista para revisión final","Faltan "&amp;REVISION!B18&amp;" controles")</x:f>
-        <x:v>Faltan 11 controles</x:v>
+        <x:v>Faltan 12 controles</x:v>
       </x:c>
       <x:c r="C5" s="34"/>
       <x:c r="D5" s="34"/>
@@ -1306,12 +1464,106 @@
         <x:v>La plantilla no sustituye la revisión profesional</x:v>
       </x:c>
     </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="44" t="str">
+        <x:v>Cierre monetario con multas</x:v>
+      </x:c>
+      <x:c r="B30" s="44"/>
+      <x:c r="C30" s="44"/>
+      <x:c r="D30" s="44"/>
+      <x:c r="E30" s="44"/>
+      <x:c r="F30" s="44"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="48" t="str">
+        <x:v>Concepto</x:v>
+      </x:c>
+      <x:c r="B31" s="48" t="str">
+        <x:v>Tratamiento</x:v>
+      </x:c>
+      <x:c r="C31" s="48" t="str">
+        <x:v>Bajo</x:v>
+      </x:c>
+      <x:c r="D31" s="48" t="str">
+        <x:v>Central</x:v>
+      </x:c>
+      <x:c r="E31" s="48" t="str">
+        <x:v>Alto</x:v>
+      </x:c>
+      <x:c r="F31" s="48" t="str">
+        <x:v>Observación</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="50" t="str">
+        <x:v>Total compatible VDTC</x:v>
+      </x:c>
+      <x:c r="B32" s="50" t="str">
+        <x:v>Daños + restauración R</x:v>
+      </x:c>
+      <x:c r="C32" s="66" t="str">
+        <x:f>IF(CASO!$E$9="Sí",C16+C14,"")</x:f>
+      </x:c>
+      <x:c r="D32" s="66" t="str">
+        <x:f>IF(CASO!$E$9="Sí",D16+D14,"")</x:f>
+      </x:c>
+      <x:c r="E32" s="66" t="str">
+        <x:f>IF(CASO!$E$9="Sí",E16+E14,"")</x:f>
+      </x:c>
+      <x:c r="F32" s="50" t="str">
+        <x:v>Solo si la agregación fue autorizada</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="50" t="str">
+        <x:v>Multas Ley 7317</x:v>
+      </x:c>
+      <x:c r="B33" s="50" t="str">
+        <x:v>Pena monetaria separada</x:v>
+      </x:c>
+      <x:c r="C33" s="66" t="n">
+        <x:f>MULTAS_7317!H5</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D33" s="66" t="n">
+        <x:f>MULTAS_7317!H6</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E33" s="66" t="n">
+        <x:f>MULTAS_7317!H7</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F33" s="50" t="str">
+        <x:v>Usa MULTAS_7317 y la conversión a la moneda del caso</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="75" t="str">
+        <x:v>TOTAL FINAL CON MULTAS</x:v>
+      </x:c>
+      <x:c r="B34" s="75" t="str">
+        <x:v>VDTC compatible + multas</x:v>
+      </x:c>
+      <x:c r="C34" s="76" t="str">
+        <x:f>IF(CASO!$E$9="Sí",SUM(C8:C14)+MULTAS_7317!H5,"")</x:f>
+      </x:c>
+      <x:c r="D34" s="76" t="str">
+        <x:f>IF(CASO!$E$9="Sí",SUM(D8:D14)+MULTAS_7317!H6,"")</x:f>
+      </x:c>
+      <x:c r="E34" s="76" t="str">
+        <x:f>IF(CASO!$E$9="Sí",SUM(E8:E14)+MULTAS_7317!H7,"")</x:f>
+      </x:c>
+      <x:c r="F34" s="75" t="str">
+        <x:v>Mantiene visible la separación metodológica</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A2:F2"/>
     <x:mergeCell ref="A3:F3"/>
     <x:mergeCell ref="A19:F19"/>
     <x:mergeCell ref="A25:F25"/>
+    <x:mergeCell ref="A30:F30"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1494,7 +1746,7 @@
         <x:v>Moneda</x:v>
       </x:c>
       <x:c r="B13" s="21" t="str">
-        <x:v>USD</x:v>
+        <x:v>CRC</x:v>
       </x:c>
       <x:c r="C13" s="34"/>
       <x:c r="D13" s="34"/>
@@ -11714,10 +11966,14 @@
       <x:c r="F16" s="34"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="34"/>
-      <x:c r="B17" s="34"/>
-      <x:c r="C17" s="34"/>
-      <x:c r="D17" s="34"/>
+      <x:c r="A17" s="50" t="str">
+        <x:v>Multas Ley 7317 seleccionadas y revisadas jurídicamente</x:v>
+      </x:c>
+      <x:c r="B17" s="60" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C17" s="50"/>
+      <x:c r="D17" s="50"/>
       <x:c r="E17" s="34"/>
       <x:c r="F17" s="34"/>
     </x:row>
@@ -11726,8 +11982,8 @@
         <x:v>Controles pendientes</x:v>
       </x:c>
       <x:c r="B18" s="29" t="n">
-        <x:f>COUNTIF(B6:B16,"No")+COUNTBLANK(B6:B16)</x:f>
-        <x:v>11</x:v>
+        <x:f>COUNTIF(B6:B17,"No")+COUNTBLANK(B6:B17)</x:f>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C18" s="34"/>
       <x:c r="D18" s="34"/>
@@ -11830,13 +12086,1859 @@
     <x:mergeCell ref="A3:F3"/>
     <x:mergeCell ref="A21:F21"/>
   </x:mergeCells>
-  <x:dataValidations count="2">
+  <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="B6:B16">
       <x:formula1>"Sí,No,No aplica"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="C23:C25">
       <x:formula1>"Pendiente,Aprobada,Devuelta"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="B17">
+      <x:formula1>"Sí,No"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="58" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="44" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="32" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="37" t="str">
+        <x:v>Multas aplicables · Ley N.° 7317</x:v>
+      </x:c>
+      <x:c r="B1" s="37"/>
+      <x:c r="C1" s="37"/>
+      <x:c r="D1" s="37"/>
+      <x:c r="E1" s="37"/>
+      <x:c r="F1" s="37"/>
+      <x:c r="G1" s="37"/>
+      <x:c r="H1" s="37"/>
+      <x:c r="I1" s="37"/>
+      <x:c r="J1" s="37"/>
+      <x:c r="K1" s="37"/>
+      <x:c r="L1" s="37"/>
+      <x:c r="M1" s="37"/>
+      <x:c r="N1" s="37"/>
+    </x:row>
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="41" t="str">
+        <x:v>Seleccione únicamente las conductas confirmadas por la revisión jurídica. Las multas se mantienen separadas del daño ambiental y se trasladan al cierre monetario del RESUMEN.</x:v>
+      </x:c>
+      <x:c r="B2" s="41"/>
+      <x:c r="C2" s="41"/>
+      <x:c r="D2" s="41"/>
+      <x:c r="E2" s="41"/>
+      <x:c r="F2" s="41"/>
+      <x:c r="G2" s="41"/>
+      <x:c r="H2" s="41"/>
+      <x:c r="I2" s="41"/>
+      <x:c r="J2" s="41"/>
+      <x:c r="K2" s="41"/>
+      <x:c r="L2" s="41"/>
+      <x:c r="M2" s="41"/>
+      <x:c r="N2" s="41"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="50" t="str">
+        <x:v>Salario base Ley 7337 (CRC)</x:v>
+      </x:c>
+      <x:c r="B4" s="62" t="n">
+        <x:v>462200</x:v>
+      </x:c>
+      <x:c r="D4" s="48" t="str">
+        <x:v>Escenario</x:v>
+      </x:c>
+      <x:c r="E4" s="48" t="str">
+        <x:v>Total en CRC</x:v>
+      </x:c>
+      <x:c r="G4" s="48" t="str">
+        <x:v>Escenario</x:v>
+      </x:c>
+      <x:c r="H4" s="48" t="str">
+        <x:v>Total en moneda del caso</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="50" t="str">
+        <x:v>Año del salario base</x:v>
+      </x:c>
+      <x:c r="B5" s="60" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D5" s="50" t="str">
+        <x:v>Bajo</x:v>
+      </x:c>
+      <x:c r="E5" s="65" t="n">
+        <x:f>SUM(K12:K46)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5" s="50" t="str">
+        <x:v>Bajo</x:v>
+      </x:c>
+      <x:c r="H5" s="66" t="n">
+        <x:f>IF($B$7&gt;0,E5/$B$7,"")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="50" t="str">
+        <x:v>Moneda del caso</x:v>
+      </x:c>
+      <x:c r="B6" s="50" t="str">
+        <x:f>CASO!B13</x:f>
+        <x:v>CRC</x:v>
+      </x:c>
+      <x:c r="D6" s="50" t="str">
+        <x:v>Central o firme</x:v>
+      </x:c>
+      <x:c r="E6" s="65" t="n">
+        <x:f>SUM(L12:L46)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="50" t="str">
+        <x:v>Central o firme</x:v>
+      </x:c>
+      <x:c r="H6" s="66" t="n">
+        <x:f>IF($B$7&gt;0,E6/$B$7,"")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="50" t="str">
+        <x:v>CRC por 1 unidad de moneda del caso</x:v>
+      </x:c>
+      <x:c r="B7" s="60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D7" s="50" t="str">
+        <x:v>Alto</x:v>
+      </x:c>
+      <x:c r="E7" s="65" t="n">
+        <x:f>SUM(M12:M46)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7" s="50" t="str">
+        <x:v>Alto</x:v>
+      </x:c>
+      <x:c r="H7" s="66" t="n">
+        <x:f>IF($B$7&gt;0,E7/$B$7,"")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="50" t="str">
+        <x:v>Fuente del salario base</x:v>
+      </x:c>
+      <x:c r="B8" s="50" t="str">
+        <x:v>Poder Judicial · salario base 2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="50" t="str">
+        <x:v>Fuente legal</x:v>
+      </x:c>
+      <x:c r="B9" s="50" t="str">
+        <x:v>PGR · texto consolidado de la Ley 7317</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="44" t="str">
+        <x:v>Seleccione las multas aplicables</x:v>
+      </x:c>
+      <x:c r="B10" s="44"/>
+      <x:c r="C10" s="44"/>
+      <x:c r="D10" s="44"/>
+      <x:c r="E10" s="44"/>
+      <x:c r="F10" s="44"/>
+      <x:c r="G10" s="44"/>
+      <x:c r="H10" s="44"/>
+      <x:c r="I10" s="44"/>
+      <x:c r="J10" s="44"/>
+      <x:c r="K10" s="44"/>
+      <x:c r="L10" s="44"/>
+      <x:c r="M10" s="44"/>
+      <x:c r="N10" s="44"/>
+    </x:row>
+    <x:row r="11" ht="48" customHeight="1">
+      <x:c r="A11" s="48" t="str">
+        <x:v>SELECCIONAR</x:v>
+      </x:c>
+      <x:c r="B11" s="48" t="str">
+        <x:v>ARTÍCULO</x:v>
+      </x:c>
+      <x:c r="C11" s="48" t="str">
+        <x:v>TIPO</x:v>
+      </x:c>
+      <x:c r="D11" s="48" t="str">
+        <x:v>CONDUCTA SANCIONADA</x:v>
+      </x:c>
+      <x:c r="E11" s="48" t="str">
+        <x:v>MÍN_SB</x:v>
+      </x:c>
+      <x:c r="F11" s="48" t="str">
+        <x:v>SB APLICADOS</x:v>
+      </x:c>
+      <x:c r="G11" s="48" t="str">
+        <x:v>MÁX_SB</x:v>
+      </x:c>
+      <x:c r="H11" s="48" t="str">
+        <x:v>MONTO FIRME CRC</x:v>
+      </x:c>
+      <x:c r="I11" s="48" t="str">
+        <x:v>OTRAS CONSECUENCIAS</x:v>
+      </x:c>
+      <x:c r="J11" s="48" t="str">
+        <x:v>FUENTE</x:v>
+      </x:c>
+      <x:c r="K11" s="48" t="str">
+        <x:v>BAJO CRC</x:v>
+      </x:c>
+      <x:c r="L11" s="48" t="str">
+        <x:v>CENTRAL/FIRME CRC</x:v>
+      </x:c>
+      <x:c r="M11" s="48" t="str">
+        <x:v>ALTO CRC</x:v>
+      </x:c>
+      <x:c r="N11" s="48" t="str">
+        <x:v>OBSERVACIONES DEL CASO</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="58" customHeight="1">
+      <x:c r="A12" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B12" s="50" t="str">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C12" s="50" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D12" s="50" t="str">
+        <x:v>Extraer o destruir, sin autorización, plantas o sus productos en áreas oficiales de protección o áreas privadas autorizadas.</x:v>
+      </x:c>
+      <x:c r="E12" s="67" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F12" s="68" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G12" s="67" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H12" s="62"/>
+      <x:c r="I12" s="50" t="str">
+        <x:v>Multa o prisión de 2 a 4 meses; comiso de las piezas.</x:v>
+      </x:c>
+      <x:c r="J12" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K12" s="63" t="n">
+        <x:f>IF($A12="☑ Sí",$E12*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L12" s="63" t="n">
+        <x:f>IF($A12="☑ Sí",IF($H12&gt;0,$H12,$F12*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M12" s="63" t="n">
+        <x:f>IF($A12="☑ Sí",$G12*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N12" s="60"/>
+    </x:row>
+    <x:row r="13" ht="58" customHeight="1">
+      <x:c r="A13" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B13" s="50" t="str">
+        <x:v>91(a)</x:v>
+      </x:c>
+      <x:c r="C13" s="50" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D13" s="50" t="str">
+        <x:v>Importar o exportar flora silvestre en peligro, con poblaciones reducidas o incluida en CITES, sin autorización.</x:v>
+      </x:c>
+      <x:c r="E13" s="67" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F13" s="68" t="n">
+        <x:v>5.5</x:v>
+      </x:c>
+      <x:c r="G13" s="67" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H13" s="62"/>
+      <x:c r="I13" s="50" t="str">
+        <x:v>Multa o prisión de 2 a 4 meses; comiso de las piezas.</x:v>
+      </x:c>
+      <x:c r="J13" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K13" s="63" t="n">
+        <x:f>IF($A13="☑ Sí",$E13*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="63" t="n">
+        <x:f>IF($A13="☑ Sí",IF($H13&gt;0,$H13,$F13*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="63" t="n">
+        <x:f>IF($A13="☑ Sí",$G13*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="60"/>
+    </x:row>
+    <x:row r="14" ht="58" customHeight="1">
+      <x:c r="A14" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B14" s="50" t="str">
+        <x:v>91(b)</x:v>
+      </x:c>
+      <x:c r="C14" s="50" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D14" s="50" t="str">
+        <x:v>Importar o exportar productos o subproductos de árboles maderables en peligro, con poblaciones reducidas e incluidos en CITES, sin autorización.</x:v>
+      </x:c>
+      <x:c r="E14" s="67" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F14" s="68" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G14" s="67" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H14" s="62"/>
+      <x:c r="I14" s="50" t="str">
+        <x:v>Multa o prisión de 3 a 6 meses.</x:v>
+      </x:c>
+      <x:c r="J14" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K14" s="63" t="n">
+        <x:f>IF($A14="☑ Sí",$E14*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L14" s="63" t="n">
+        <x:f>IF($A14="☑ Sí",IF($H14&gt;0,$H14,$F14*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" s="63" t="n">
+        <x:f>IF($A14="☑ Sí",$G14*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N14" s="60"/>
+    </x:row>
+    <x:row r="15" ht="58" customHeight="1">
+      <x:c r="A15" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B15" s="50" t="str">
+        <x:v>91(c)</x:v>
+      </x:c>
+      <x:c r="C15" s="50" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D15" s="50" t="str">
+        <x:v>Importar o exportar plantas que no están en peligro de extinción, sin autorización.</x:v>
+      </x:c>
+      <x:c r="E15" s="67" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F15" s="68" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G15" s="67" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="H15" s="62"/>
+      <x:c r="I15" s="50" t="str">
+        <x:v>Multa equivalente al 50 % del rango de 1 a 3 salarios base, o prisión de 1 a 3 meses; comiso.</x:v>
+      </x:c>
+      <x:c r="J15" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K15" s="63" t="n">
+        <x:f>IF($A15="☑ Sí",$E15*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L15" s="63" t="n">
+        <x:f>IF($A15="☑ Sí",IF($H15&gt;0,$H15,$F15*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="63" t="n">
+        <x:f>IF($A15="☑ Sí",$G15*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="60"/>
+    </x:row>
+    <x:row r="16" ht="58" customHeight="1">
+      <x:c r="A16" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B16" s="50" t="str">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C16" s="50" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D16" s="50" t="str">
+        <x:v>Comerciar, negociar, traficar o trasegar flora protegida, sus productos o subproductos, sin permiso.</x:v>
+      </x:c>
+      <x:c r="E16" s="67" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F16" s="68" t="n">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="G16" s="67" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H16" s="62"/>
+      <x:c r="I16" s="50" t="str">
+        <x:v>Multa o prisión de 3 a 6 meses; comiso.</x:v>
+      </x:c>
+      <x:c r="J16" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K16" s="63" t="n">
+        <x:f>IF($A16="☑ Sí",$E16*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16" s="63" t="n">
+        <x:f>IF($A16="☑ Sí",IF($H16&gt;0,$H16,$F16*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="63" t="n">
+        <x:f>IF($A16="☑ Sí",$G16*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16" s="60"/>
+    </x:row>
+    <x:row r="17" ht="58" customHeight="1">
+      <x:c r="A17" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B17" s="50" t="str">
+        <x:v>93(b)</x:v>
+      </x:c>
+      <x:c r="C17" s="50" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D17" s="50" t="str">
+        <x:v>Cazar o capturar fauna no amenazada en áreas oficiales o privadas autorizadas, o individuos incluidos en investigación autorizada.</x:v>
+      </x:c>
+      <x:c r="E17" s="67" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F17" s="68" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G17" s="67" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H17" s="62"/>
+      <x:c r="I17" s="50" t="str">
+        <x:v>Multa o prisión de 6 meses a 1 año; comiso de equipo y piezas.</x:v>
+      </x:c>
+      <x:c r="J17" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K17" s="63" t="n">
+        <x:f>IF($A17="☑ Sí",$E17*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="63" t="n">
+        <x:f>IF($A17="☑ Sí",IF($H17&gt;0,$H17,$F17*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="63" t="n">
+        <x:f>IF($A17="☑ Sí",$G17*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N17" s="60"/>
+    </x:row>
+    <x:row r="18" ht="58" customHeight="1">
+      <x:c r="A18" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B18" s="50" t="str">
+        <x:v>93(c)</x:v>
+      </x:c>
+      <x:c r="C18" s="50" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D18" s="50" t="str">
+        <x:v>Cazar fauna sujeta a veda que no esté comprendida en los incisos anteriores.</x:v>
+      </x:c>
+      <x:c r="E18" s="67" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F18" s="68" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G18" s="67" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H18" s="62"/>
+      <x:c r="I18" s="50" t="str">
+        <x:v>Multa o prisión de 2 a 4 meses; comiso de armas y piezas.</x:v>
+      </x:c>
+      <x:c r="J18" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K18" s="63" t="n">
+        <x:f>IF($A18="☑ Sí",$E18*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L18" s="63" t="n">
+        <x:f>IF($A18="☑ Sí",IF($H18&gt;0,$H18,$F18*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18" s="63" t="n">
+        <x:f>IF($A18="☑ Sí",$G18*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N18" s="60"/>
+    </x:row>
+    <x:row r="19" ht="58" customHeight="1">
+      <x:c r="A19" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B19" s="50" t="str">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C19" s="50" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D19" s="50" t="str">
+        <x:v>Usar sin autorización venenos, materiales peligrosos, explosivos, plaguicidas u otro método capaz de eliminar fauna y poner en peligro su subsistencia regional.</x:v>
+      </x:c>
+      <x:c r="E19" s="67" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F19" s="68" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G19" s="67" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H19" s="62"/>
+      <x:c r="I19" s="50" t="str">
+        <x:v>Multa o prisión de 1 a 2 años; pérdida del equipo o material; salvo delito más grave.</x:v>
+      </x:c>
+      <x:c r="J19" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K19" s="63" t="n">
+        <x:f>IF($A19="☑ Sí",$E19*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L19" s="63" t="n">
+        <x:f>IF($A19="☑ Sí",IF($H19&gt;0,$H19,$F19*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M19" s="63" t="n">
+        <x:f>IF($A19="☑ Sí",$G19*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N19" s="60"/>
+    </x:row>
+    <x:row r="20" ht="58" customHeight="1">
+      <x:c r="A20" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B20" s="50" t="str">
+        <x:v>95(a)</x:v>
+      </x:c>
+      <x:c r="C20" s="50" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D20" s="50" t="str">
+        <x:v>Comerciar, negociar, traficar o trasegar fauna en peligro o con poblaciones reducidas, sus productos o derivados, sin permiso.</x:v>
+      </x:c>
+      <x:c r="E20" s="67" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F20" s="68" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G20" s="67" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H20" s="62"/>
+      <x:c r="I20" s="50" t="str">
+        <x:v>Multa o prisión de 1 a 3 años; comiso.</x:v>
+      </x:c>
+      <x:c r="J20" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K20" s="63" t="n">
+        <x:f>IF($A20="☑ Sí",$E20*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L20" s="63" t="n">
+        <x:f>IF($A20="☑ Sí",IF($H20&gt;0,$H20,$F20*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M20" s="63" t="n">
+        <x:f>IF($A20="☑ Sí",$G20*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N20" s="60"/>
+    </x:row>
+    <x:row r="21" ht="58" customHeight="1">
+      <x:c r="A21" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B21" s="50" t="str">
+        <x:v>95(b)</x:v>
+      </x:c>
+      <x:c r="C21" s="50" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D21" s="50" t="str">
+        <x:v>Comerciar, negociar, traficar o trasegar fauna no amenazada, sus productos o derivados, sin permiso.</x:v>
+      </x:c>
+      <x:c r="E21" s="67" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F21" s="68" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G21" s="67" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H21" s="62"/>
+      <x:c r="I21" s="50" t="str">
+        <x:v>Multa o prisión de 4 a 6 meses; comiso.</x:v>
+      </x:c>
+      <x:c r="J21" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K21" s="63" t="n">
+        <x:f>IF($A21="☑ Sí",$E21*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L21" s="63" t="n">
+        <x:f>IF($A21="☑ Sí",IF($H21&gt;0,$H21,$F21*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M21" s="63" t="n">
+        <x:f>IF($A21="☑ Sí",$G21*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N21" s="60"/>
+    </x:row>
+    <x:row r="22" ht="58" customHeight="1">
+      <x:c r="A22" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B22" s="50" t="str">
+        <x:v>96(a)</x:v>
+      </x:c>
+      <x:c r="C22" s="50" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D22" s="50" t="str">
+        <x:v>Importar o exportar fauna en peligro, con poblaciones reducidas o incluida en CITES, sus productos o derivados, sin permiso.</x:v>
+      </x:c>
+      <x:c r="E22" s="67" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F22" s="68" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G22" s="67" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H22" s="62"/>
+      <x:c r="I22" s="50" t="str">
+        <x:v>Multa o prisión de 1 a 3 años; comiso.</x:v>
+      </x:c>
+      <x:c r="J22" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K22" s="63" t="n">
+        <x:f>IF($A22="☑ Sí",$E22*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L22" s="63" t="n">
+        <x:f>IF($A22="☑ Sí",IF($H22&gt;0,$H22,$F22*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M22" s="63" t="n">
+        <x:f>IF($A22="☑ Sí",$G22*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N22" s="60"/>
+    </x:row>
+    <x:row r="23" ht="58" customHeight="1">
+      <x:c r="A23" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B23" s="50" t="str">
+        <x:v>96(b)</x:v>
+      </x:c>
+      <x:c r="C23" s="50" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D23" s="50" t="str">
+        <x:v>Importar o exportar fauna no amenazada, sus productos o derivados, sin permiso.</x:v>
+      </x:c>
+      <x:c r="E23" s="67" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F23" s="68" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G23" s="67" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H23" s="62"/>
+      <x:c r="I23" s="50" t="str">
+        <x:v>Multa o prisión de 4 a 8 meses; comiso.</x:v>
+      </x:c>
+      <x:c r="J23" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K23" s="63" t="n">
+        <x:f>IF($A23="☑ Sí",$E23*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L23" s="63" t="n">
+        <x:f>IF($A23="☑ Sí",IF($H23&gt;0,$H23,$F23*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M23" s="63" t="n">
+        <x:f>IF($A23="☑ Sí",$G23*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N23" s="60"/>
+    </x:row>
+    <x:row r="24" ht="58" customHeight="1">
+      <x:c r="A24" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B24" s="50" t="str">
+        <x:v>97, párr. 1</x:v>
+      </x:c>
+      <x:c r="C24" s="50" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D24" s="50" t="str">
+        <x:v>Pescar en aguas continentales con explosivos, arbaletas, atarrayas, chinchorros, líneas múltiples, trasmallo u otro método que ponga en peligro la continuidad de las especies.</x:v>
+      </x:c>
+      <x:c r="E24" s="67" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F24" s="68" t="n">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="G24" s="67" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H24" s="62"/>
+      <x:c r="I24" s="50" t="str">
+        <x:v>Multa o prisión de 2 a 8 meses; comiso del equipo o material.</x:v>
+      </x:c>
+      <x:c r="J24" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K24" s="63" t="n">
+        <x:f>IF($A24="☑ Sí",$E24*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L24" s="63" t="n">
+        <x:f>IF($A24="☑ Sí",IF($H24&gt;0,$H24,$F24*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M24" s="63" t="n">
+        <x:f>IF($A24="☑ Sí",$G24*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N24" s="60"/>
+    </x:row>
+    <x:row r="25" ht="58" customHeight="1">
+      <x:c r="A25" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B25" s="50" t="str">
+        <x:v>97, párr. 2</x:v>
+      </x:c>
+      <x:c r="C25" s="50" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D25" s="50" t="str">
+        <x:v>Pescar en aguas continentales con venenos, cal o plaguicidas.</x:v>
+      </x:c>
+      <x:c r="E25" s="67" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F25" s="68" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G25" s="67" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H25" s="62"/>
+      <x:c r="I25" s="50" t="str">
+        <x:v>Multa o prisión de 1 a 2 años; comiso; salvo delito más grave.</x:v>
+      </x:c>
+      <x:c r="J25" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K25" s="63" t="n">
+        <x:f>IF($A25="☑ Sí",$E25*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L25" s="63" t="n">
+        <x:f>IF($A25="☑ Sí",IF($H25&gt;0,$H25,$F25*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M25" s="63" t="n">
+        <x:f>IF($A25="☑ Sí",$G25*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N25" s="60"/>
+    </x:row>
+    <x:row r="26" ht="58" customHeight="1">
+      <x:c r="A26" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B26" s="50" t="str">
+        <x:v>97, párr. final</x:v>
+      </x:c>
+      <x:c r="C26" s="50" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D26" s="50" t="str">
+        <x:v>Dañar poblaciones objetivo de pesca, especies capturadas incidentalmente o ecosistemas de los que dependen.</x:v>
+      </x:c>
+      <x:c r="E26" s="67" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F26" s="68" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G26" s="67" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H26" s="62"/>
+      <x:c r="I26" s="50" t="str">
+        <x:v>La norma remite a igual pena del párrafo anterior; confirmar la calificación jurídica del caso.</x:v>
+      </x:c>
+      <x:c r="J26" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K26" s="63" t="n">
+        <x:f>IF($A26="☑ Sí",$E26*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L26" s="63" t="n">
+        <x:f>IF($A26="☑ Sí",IF($H26&gt;0,$H26,$F26*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M26" s="63" t="n">
+        <x:f>IF($A26="☑ Sí",$G26*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N26" s="60"/>
+    </x:row>
+    <x:row r="27" ht="58" customHeight="1">
+      <x:c r="A27" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B27" s="50" t="str">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C27" s="50" t="str">
+        <x:v>Delito</x:v>
+      </x:c>
+      <x:c r="D27" s="50" t="str">
+        <x:v>Introducir o liberar sin autorización especies exóticas o materiales de control biológico que pongan en peligro la conservación de flora o fauna.</x:v>
+      </x:c>
+      <x:c r="E27" s="67" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F27" s="68" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G27" s="67" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H27" s="62"/>
+      <x:c r="I27" s="50" t="str">
+        <x:v>Multa o prisión de 1 a 2 años; pérdida del equipo o material; salvo delito más grave.</x:v>
+      </x:c>
+      <x:c r="J27" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K27" s="63" t="n">
+        <x:f>IF($A27="☑ Sí",$E27*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L27" s="63" t="n">
+        <x:f>IF($A27="☑ Sí",IF($H27&gt;0,$H27,$F27*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M27" s="63" t="n">
+        <x:f>IF($A27="☑ Sí",$G27*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N27" s="60"/>
+    </x:row>
+    <x:row r="28" ht="58" customHeight="1">
+      <x:c r="A28" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B28" s="50" t="str">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C28" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D28" s="50" t="str">
+        <x:v>Extraer sin autorización plantas o productos, sin fin comercial, en áreas oficiales de protección o áreas privadas autorizadas.</x:v>
+      </x:c>
+      <x:c r="E28" s="67" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="F28" s="68" t="n">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="G28" s="67" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H28" s="62"/>
+      <x:c r="I28" s="50" t="str">
+        <x:v>Multa y comiso de las piezas.</x:v>
+      </x:c>
+      <x:c r="J28" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K28" s="63" t="n">
+        <x:f>IF($A28="☑ Sí",$E28*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L28" s="63" t="n">
+        <x:f>IF($A28="☑ Sí",IF($H28&gt;0,$H28,$F28*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M28" s="63" t="n">
+        <x:f>IF($A28="☑ Sí",$G28*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N28" s="60"/>
+    </x:row>
+    <x:row r="29" ht="58" customHeight="1">
+      <x:c r="A29" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B29" s="50" t="str">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C29" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D29" s="50" t="str">
+        <x:v>Extraer o comerciar sin autorización raíces o tallos de helechos arborescentes.</x:v>
+      </x:c>
+      <x:c r="E29" s="67" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F29" s="68" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="G29" s="67" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H29" s="62"/>
+      <x:c r="I29" s="50" t="str">
+        <x:v>Multa.</x:v>
+      </x:c>
+      <x:c r="J29" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K29" s="63" t="n">
+        <x:f>IF($A29="☑ Sí",$E29*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L29" s="63" t="n">
+        <x:f>IF($A29="☑ Sí",IF($H29&gt;0,$H29,$F29*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M29" s="63" t="n">
+        <x:f>IF($A29="☑ Sí",$G29*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N29" s="60"/>
+    </x:row>
+    <x:row r="30" ht="58" customHeight="1">
+      <x:c r="A30" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B30" s="50" t="str">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C30" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D30" s="50" t="str">
+        <x:v>Extraer o comerciar flora silvestre sin autorización, cuando no exista infracción de mayor gravedad.</x:v>
+      </x:c>
+      <x:c r="E30" s="67" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="F30" s="68" t="n">
+        <x:v>0.225</x:v>
+      </x:c>
+      <x:c r="G30" s="67" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="H30" s="62"/>
+      <x:c r="I30" s="50" t="str">
+        <x:v>Multa y comiso de las piezas.</x:v>
+      </x:c>
+      <x:c r="J30" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K30" s="63" t="n">
+        <x:f>IF($A30="☑ Sí",$E30*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L30" s="63" t="n">
+        <x:f>IF($A30="☑ Sí",IF($H30&gt;0,$H30,$F30*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M30" s="63" t="n">
+        <x:f>IF($A30="☑ Sí",$G30*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N30" s="60"/>
+    </x:row>
+    <x:row r="31" ht="58" customHeight="1">
+      <x:c r="A31" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B31" s="50" t="str">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C31" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D31" s="50" t="str">
+        <x:v>Importar flora silvestre exótica sin autorización.</x:v>
+      </x:c>
+      <x:c r="E31" s="67" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="F31" s="68" t="n">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="G31" s="67" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H31" s="62"/>
+      <x:c r="I31" s="50" t="str">
+        <x:v>Multa y comiso de las piezas.</x:v>
+      </x:c>
+      <x:c r="J31" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K31" s="63" t="n">
+        <x:f>IF($A31="☑ Sí",$E31*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L31" s="63" t="n">
+        <x:f>IF($A31="☑ Sí",IF($H31&gt;0,$H31,$F31*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M31" s="63" t="n">
+        <x:f>IF($A31="☑ Sí",$G31*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N31" s="60"/>
+    </x:row>
+    <x:row r="32" ht="58" customHeight="1">
+      <x:c r="A32" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B32" s="50" t="str">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C32" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D32" s="50" t="str">
+        <x:v>Ingresar sin autorización a áreas de conservación portando armas, herramientas o utensilios útiles para caza, pesca, tala, extracción, captura o trasiego, cuando no haya infracción más grave.</x:v>
+      </x:c>
+      <x:c r="E32" s="67" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F32" s="68" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G32" s="67" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H32" s="62"/>
+      <x:c r="I32" s="50" t="str">
+        <x:v>Multa.</x:v>
+      </x:c>
+      <x:c r="J32" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K32" s="63" t="n">
+        <x:f>IF($A32="☑ Sí",$E32*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L32" s="63" t="n">
+        <x:f>IF($A32="☑ Sí",IF($H32&gt;0,$H32,$F32*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M32" s="63" t="n">
+        <x:f>IF($A32="☑ Sí",$G32*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N32" s="60"/>
+    </x:row>
+    <x:row r="33" ht="58" customHeight="1">
+      <x:c r="A33" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B33" s="50" t="str">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C33" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D33" s="50" t="str">
+        <x:v>Cazar fauna silvestre sin la licencia correspondiente.</x:v>
+      </x:c>
+      <x:c r="E33" s="67" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F33" s="68" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="G33" s="67" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H33" s="62"/>
+      <x:c r="I33" s="50" t="str">
+        <x:v>Multa; pérdida de armas y comiso de piezas.</x:v>
+      </x:c>
+      <x:c r="J33" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K33" s="63" t="n">
+        <x:f>IF($A33="☑ Sí",$E33*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L33" s="63" t="n">
+        <x:f>IF($A33="☑ Sí",IF($H33&gt;0,$H33,$F33*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M33" s="63" t="n">
+        <x:f>IF($A33="☑ Sí",$G33*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N33" s="60"/>
+    </x:row>
+    <x:row r="34" ht="58" customHeight="1">
+      <x:c r="A34" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B34" s="50" t="str">
+        <x:v>108, párr. 1</x:v>
+      </x:c>
+      <x:c r="C34" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D34" s="50" t="str">
+        <x:v>Cazar especies permitidas con armas o proyectiles inadecuados.</x:v>
+      </x:c>
+      <x:c r="E34" s="67" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F34" s="68" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="G34" s="67" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H34" s="62"/>
+      <x:c r="I34" s="50" t="str">
+        <x:v>Multa; comiso de armas y piezas.</x:v>
+      </x:c>
+      <x:c r="J34" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K34" s="63" t="n">
+        <x:f>IF($A34="☑ Sí",$E34*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L34" s="63" t="n">
+        <x:f>IF($A34="☑ Sí",IF($H34&gt;0,$H34,$F34*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M34" s="63" t="n">
+        <x:f>IF($A34="☑ Sí",$G34*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N34" s="60"/>
+    </x:row>
+    <x:row r="35" ht="58" customHeight="1">
+      <x:c r="A35" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B35" s="50" t="str">
+        <x:v>108, párr. 2</x:v>
+      </x:c>
+      <x:c r="C35" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D35" s="50" t="str">
+        <x:v>No reportar ante SINAC las piezas cazadas, pese a contar con autorización para cazar.</x:v>
+      </x:c>
+      <x:c r="E35" s="67" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F35" s="68" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="G35" s="67" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H35" s="62"/>
+      <x:c r="I35" s="50" t="str">
+        <x:v>Igual pena del párrafo anterior.</x:v>
+      </x:c>
+      <x:c r="J35" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K35" s="63" t="n">
+        <x:f>IF($A35="☑ Sí",$E35*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L35" s="63" t="n">
+        <x:f>IF($A35="☑ Sí",IF($H35&gt;0,$H35,$F35*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M35" s="63" t="n">
+        <x:f>IF($A35="☑ Sí",$G35*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N35" s="60"/>
+    </x:row>
+    <x:row r="36" ht="58" customHeight="1">
+      <x:c r="A36" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B36" s="50" t="str">
+        <x:v>109, párr. 1</x:v>
+      </x:c>
+      <x:c r="C36" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D36" s="50" t="str">
+        <x:v>Exceder los límites reglamentarios de un permiso de caza de control o pesca respecto de piezas, tamaños, especies o zonas.</x:v>
+      </x:c>
+      <x:c r="E36" s="67" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F36" s="68" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="G36" s="67" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H36" s="62"/>
+      <x:c r="I36" s="50" t="str">
+        <x:v>Multa; comiso de piezas o derivados y pérdida del equipo o material.</x:v>
+      </x:c>
+      <x:c r="J36" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K36" s="63" t="n">
+        <x:f>IF($A36="☑ Sí",$E36*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L36" s="63" t="n">
+        <x:f>IF($A36="☑ Sí",IF($H36&gt;0,$H36,$F36*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M36" s="63" t="n">
+        <x:f>IF($A36="☑ Sí",$G36*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N36" s="60"/>
+    </x:row>
+    <x:row r="37" ht="58" customHeight="1">
+      <x:c r="A37" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B37" s="50" t="str">
+        <x:v>109, párr. 2</x:v>
+      </x:c>
+      <x:c r="C37" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D37" s="50" t="str">
+        <x:v>Usar para fines distintos las piezas obtenidas con permisos de caza de subsistencia o control, o de colecta científica.</x:v>
+      </x:c>
+      <x:c r="E37" s="67" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F37" s="68" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="G37" s="67" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H37" s="62"/>
+      <x:c r="I37" s="50" t="str">
+        <x:v>Igual pena del párrafo anterior.</x:v>
+      </x:c>
+      <x:c r="J37" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K37" s="63" t="n">
+        <x:f>IF($A37="☑ Sí",$E37*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L37" s="63" t="n">
+        <x:f>IF($A37="☑ Sí",IF($H37&gt;0,$H37,$F37*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M37" s="63" t="n">
+        <x:f>IF($A37="☑ Sí",$G37*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N37" s="60"/>
+    </x:row>
+    <x:row r="38" ht="58" customHeight="1">
+      <x:c r="A38" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B38" s="50" t="str">
+        <x:v>110, supuesto 1</x:v>
+      </x:c>
+      <x:c r="C38" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D38" s="50" t="str">
+        <x:v>Mantener en cautiverio o como mascota, sin autorización, fauna en peligro de extinción o con poblaciones reducidas.</x:v>
+      </x:c>
+      <x:c r="E38" s="67" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F38" s="68" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G38" s="67" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H38" s="62"/>
+      <x:c r="I38" s="50" t="str">
+        <x:v>Multa y comiso de los animales.</x:v>
+      </x:c>
+      <x:c r="J38" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K38" s="63" t="n">
+        <x:f>IF($A38="☑ Sí",$E38*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L38" s="63" t="n">
+        <x:f>IF($A38="☑ Sí",IF($H38&gt;0,$H38,$F38*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M38" s="63" t="n">
+        <x:f>IF($A38="☑ Sí",$G38*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N38" s="60"/>
+    </x:row>
+    <x:row r="39" ht="58" customHeight="1">
+      <x:c r="A39" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B39" s="50" t="str">
+        <x:v>110, supuesto 2</x:v>
+      </x:c>
+      <x:c r="C39" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D39" s="50" t="str">
+        <x:v>Mantener en cautiverio o como mascota, sin autorización, fauna no amenazada ni con poblaciones reducidas.</x:v>
+      </x:c>
+      <x:c r="E39" s="67" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F39" s="68" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="G39" s="67" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H39" s="62"/>
+      <x:c r="I39" s="50" t="str">
+        <x:v>Multa y comiso de los animales.</x:v>
+      </x:c>
+      <x:c r="J39" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K39" s="63" t="n">
+        <x:f>IF($A39="☑ Sí",$E39*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L39" s="63" t="n">
+        <x:f>IF($A39="☑ Sí",IF($H39&gt;0,$H39,$F39*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M39" s="63" t="n">
+        <x:f>IF($A39="☑ Sí",$G39*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N39" s="60"/>
+    </x:row>
+    <x:row r="40" ht="58" customHeight="1">
+      <x:c r="A40" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B40" s="50" t="str">
+        <x:v>111, párr. 1</x:v>
+      </x:c>
+      <x:c r="C40" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D40" s="50" t="str">
+        <x:v>Dedicarse comercialmente a la taxidermia o al procesamiento de pieles de fauna silvestre sin autorización.</x:v>
+      </x:c>
+      <x:c r="E40" s="67" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="F40" s="68" t="n">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="G40" s="67" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H40" s="62"/>
+      <x:c r="I40" s="50" t="str">
+        <x:v>Multa.</x:v>
+      </x:c>
+      <x:c r="J40" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K40" s="63" t="n">
+        <x:f>IF($A40="☑ Sí",$E40*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L40" s="63" t="n">
+        <x:f>IF($A40="☑ Sí",IF($H40&gt;0,$H40,$F40*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M40" s="63" t="n">
+        <x:f>IF($A40="☑ Sí",$G40*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N40" s="60"/>
+    </x:row>
+    <x:row r="41" ht="58" customHeight="1">
+      <x:c r="A41" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B41" s="50" t="str">
+        <x:v>111, párr. 2</x:v>
+      </x:c>
+      <x:c r="C41" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D41" s="50" t="str">
+        <x:v>No llevar el libro de control exigido para taxidermia o procesamiento comercial autorizado.</x:v>
+      </x:c>
+      <x:c r="E41" s="67" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="F41" s="68" t="n">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="G41" s="67" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H41" s="62"/>
+      <x:c r="I41" s="50" t="str">
+        <x:v>Igual sanción del párrafo anterior.</x:v>
+      </x:c>
+      <x:c r="J41" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K41" s="63" t="n">
+        <x:f>IF($A41="☑ Sí",$E41*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L41" s="63" t="n">
+        <x:f>IF($A41="☑ Sí",IF($H41&gt;0,$H41,$F41*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M41" s="63" t="n">
+        <x:f>IF($A41="☑ Sí",$G41*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N41" s="60"/>
+    </x:row>
+    <x:row r="42" ht="58" customHeight="1">
+      <x:c r="A42" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B42" s="50" t="str">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C42" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D42" s="50" t="str">
+        <x:v>Dejar voluntariamente de buscar las piezas cazadas o pescadas y provocar desperdicio del recurso.</x:v>
+      </x:c>
+      <x:c r="E42" s="67" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="F42" s="68" t="n">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="G42" s="67" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H42" s="62"/>
+      <x:c r="I42" s="50" t="str">
+        <x:v>Multa.</x:v>
+      </x:c>
+      <x:c r="J42" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K42" s="63" t="n">
+        <x:f>IF($A42="☑ Sí",$E42*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L42" s="63" t="n">
+        <x:f>IF($A42="☑ Sí",IF($H42&gt;0,$H42,$F42*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M42" s="63" t="n">
+        <x:f>IF($A42="☑ Sí",$G42*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N42" s="60"/>
+    </x:row>
+    <x:row r="43" ht="58" customHeight="1">
+      <x:c r="A43" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B43" s="50" t="str">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C43" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D43" s="50" t="str">
+        <x:v>Pescar sin la licencia correspondiente.</x:v>
+      </x:c>
+      <x:c r="E43" s="67" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F43" s="68" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="G43" s="67" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H43" s="62"/>
+      <x:c r="I43" s="50" t="str">
+        <x:v>Multa; pérdida del equipo señalado y comiso de piezas.</x:v>
+      </x:c>
+      <x:c r="J43" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K43" s="63" t="n">
+        <x:f>IF($A43="☑ Sí",$E43*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L43" s="63" t="n">
+        <x:f>IF($A43="☑ Sí",IF($H43&gt;0,$H43,$F43*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M43" s="63" t="n">
+        <x:f>IF($A43="☑ Sí",$G43*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N43" s="60"/>
+    </x:row>
+    <x:row r="44" ht="58" customHeight="1">
+      <x:c r="A44" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B44" s="50" t="str">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C44" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D44" s="50" t="str">
+        <x:v>Exceder límites de pesca respecto de tamaños, cantidades, especies o zonas autorizadas.</x:v>
+      </x:c>
+      <x:c r="E44" s="67" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="F44" s="68" t="n">
+        <x:v>0.225</x:v>
+      </x:c>
+      <x:c r="G44" s="67" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="H44" s="62"/>
+      <x:c r="I44" s="50" t="str">
+        <x:v>Multa.</x:v>
+      </x:c>
+      <x:c r="J44" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K44" s="63" t="n">
+        <x:f>IF($A44="☑ Sí",$E44*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L44" s="63" t="n">
+        <x:f>IF($A44="☑ Sí",IF($H44&gt;0,$H44,$F44*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M44" s="63" t="n">
+        <x:f>IF($A44="☑ Sí",$G44*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N44" s="60"/>
+    </x:row>
+    <x:row r="45" ht="58" customHeight="1">
+      <x:c r="A45" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B45" s="50" t="str">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="C45" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D45" s="50" t="str">
+        <x:v>Pescar en tiempo de veda.</x:v>
+      </x:c>
+      <x:c r="E45" s="67" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F45" s="68" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="G45" s="67" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H45" s="62"/>
+      <x:c r="I45" s="50" t="str">
+        <x:v>Multa y comiso del equipo y las piezas.</x:v>
+      </x:c>
+      <x:c r="J45" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K45" s="63" t="n">
+        <x:f>IF($A45="☑ Sí",$E45*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L45" s="63" t="n">
+        <x:f>IF($A45="☑ Sí",IF($H45&gt;0,$H45,$F45*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M45" s="63" t="n">
+        <x:f>IF($A45="☑ Sí",$G45*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N45" s="60"/>
+    </x:row>
+    <x:row r="46" ht="58" customHeight="1">
+      <x:c r="A46" s="60" t="str">
+        <x:v>☐ No</x:v>
+      </x:c>
+      <x:c r="B46" s="50" t="str">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C46" s="50" t="str">
+        <x:v>Contravención</x:v>
+      </x:c>
+      <x:c r="D46" s="50" t="str">
+        <x:v>Suministrar sin autorización alimentos o sustancias no autorizadas a la fauna silvestre.</x:v>
+      </x:c>
+      <x:c r="E46" s="67" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="F46" s="68" t="n">
+        <x:v>0.225</x:v>
+      </x:c>
+      <x:c r="G46" s="67" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="H46" s="62"/>
+      <x:c r="I46" s="50" t="str">
+        <x:v>Multa.</x:v>
+      </x:c>
+      <x:c r="J46" s="50" t="str">
+        <x:v>Ley 7317, texto consolidado PGR</x:v>
+      </x:c>
+      <x:c r="K46" s="63" t="n">
+        <x:f>IF($A46="☑ Sí",$E46*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L46" s="63" t="n">
+        <x:f>IF($A46="☑ Sí",IF($H46&gt;0,$H46,$F46*$B$4),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M46" s="63" t="n">
+        <x:f>IF($A46="☑ Sí",$G46*$B$4,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N46" s="60"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="55" t="str">
+        <x:v>TOTAL MULTAS SELECCIONADAS</x:v>
+      </x:c>
+      <x:c r="B47" s="55"/>
+      <x:c r="C47" s="55"/>
+      <x:c r="D47" s="55"/>
+      <x:c r="E47" s="55"/>
+      <x:c r="F47" s="55"/>
+      <x:c r="G47" s="55"/>
+      <x:c r="H47" s="55"/>
+      <x:c r="I47" s="55"/>
+      <x:c r="J47" s="55"/>
+      <x:c r="K47" s="64" t="n">
+        <x:f>SUM(K12:K46)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L47" s="64" t="n">
+        <x:f>SUM(L12:L46)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M47" s="64" t="n">
+        <x:f>SUM(M12:M46)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N47" s="55" t="str">
+        <x:v>Confirmar selección y cuantía con la revisión jurídica.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="44" t="str">
+        <x:v>Fuentes oficiales</x:v>
+      </x:c>
+      <x:c r="B49" s="44"/>
+      <x:c r="C49" s="44"/>
+      <x:c r="D49" s="44"/>
+      <x:c r="E49" s="44"/>
+      <x:c r="F49" s="44"/>
+      <x:c r="G49" s="44"/>
+      <x:c r="H49" s="44"/>
+      <x:c r="I49" s="44"/>
+      <x:c r="J49" s="44"/>
+      <x:c r="K49" s="44"/>
+      <x:c r="L49" s="44"/>
+      <x:c r="M49" s="44"/>
+      <x:c r="N49" s="44"/>
+    </x:row>
+    <x:row r="50" ht="34" customHeight="1">
+      <x:c r="A50" s="50" t="str">
+        <x:v>Ley 7317</x:v>
+      </x:c>
+      <x:c r="B50" s="50" t="str">
+        <x:v>https://pgrweb.go.cr/scij/Busqueda/Normativa/normas/nrm_texto_completo.aspx?nValor1=1&amp;nValor2=12648&amp;nValor3=122136&amp;nValor4=NO&amp;param2=2&amp;strTipM=TC</x:v>
+      </x:c>
+      <x:c r="C50" s="50"/>
+      <x:c r="D50" s="50"/>
+      <x:c r="E50" s="50"/>
+      <x:c r="F50" s="50"/>
+      <x:c r="G50" s="50"/>
+      <x:c r="H50" s="50"/>
+      <x:c r="I50" s="50"/>
+      <x:c r="J50" s="50"/>
+      <x:c r="K50" s="50"/>
+      <x:c r="L50" s="50"/>
+      <x:c r="M50" s="50"/>
+      <x:c r="N50" s="50"/>
+    </x:row>
+    <x:row r="51" ht="34" customHeight="1">
+      <x:c r="A51" s="50" t="str">
+        <x:v>Salario base 2026</x:v>
+      </x:c>
+      <x:c r="B51" s="50" t="str">
+        <x:v>https://pj.poder-judicial.go.cr/index.php/component/content/article/2333-poder-judicial-fija-en-462-200-00-el-salario-base-para-multas-y-penas-por-la-comision-de-figuras-delictivas-en-el-2026?Itemid=409&amp;catid=8</x:v>
+      </x:c>
+      <x:c r="C51" s="50"/>
+      <x:c r="D51" s="50"/>
+      <x:c r="E51" s="50"/>
+      <x:c r="F51" s="50"/>
+      <x:c r="G51" s="50"/>
+      <x:c r="H51" s="50"/>
+      <x:c r="I51" s="50"/>
+      <x:c r="J51" s="50"/>
+      <x:c r="K51" s="50"/>
+      <x:c r="L51" s="50"/>
+      <x:c r="M51" s="50"/>
+      <x:c r="N51" s="50"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:N1"/>
+    <x:mergeCell ref="A2:N2"/>
+    <x:mergeCell ref="A10:N10"/>
+    <x:mergeCell ref="A47:J47"/>
+    <x:mergeCell ref="A49:N49"/>
+    <x:mergeCell ref="B50:N50"/>
+    <x:mergeCell ref="B51:N51"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="A12:N46">
+    <x:cfRule type="expression" dxfId="0" priority="1">
+      <x:formula>$A12="☑ Sí"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:dataValidations count="3">
+    <x:dataValidation type="list" sqref="A12:A46">
+      <x:formula1>"☐ No,☑ Sí"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="F12:F46">
+      <x:formula1>0</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="H12:H46">
+      <x:formula1>0</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
